--- a/assets/data/excel/equipment.xlsx
+++ b/assets/data/excel/equipment.xlsx
@@ -1,7 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="装备列表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="强化等级" sheetId="2" state="visible" r:id="rId2"/>
@@ -9,55 +13,31 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掉落来源" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -65,32 +45,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -237,7 +202,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -272,7 +236,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -307,16 +270,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -438,46 +405,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -488,188 +416,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>equipId</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>rarity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>atkBonus</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>hpBonus</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>critRateBonus</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>dodgeRateBonus</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>damageReductionBonus</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>装备ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>品质</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>稀有度</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>攻击加成</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>生命加成</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>暴击率加成</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>闪避率加成</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>减伤加成</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -678,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WPN002</t>
+          <t>WPN001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>制式军刀</t>
+          <t>生锈军刀</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -693,14 +608,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -716,19 +631,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>标准配置的军用武器</t>
+          <t>废土上随处可见的旧式武器</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WPN001</t>
+          <t>WPN002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>生锈长剑</t>
+          <t>制式军刀</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -738,14 +653,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -761,7 +676,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>一把普通的生锈长剑</t>
+          <t>标准配置的军用武器</t>
         </is>
       </c>
     </row>
@@ -773,7 +688,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>能量光剑</t>
+          <t>能量光刃</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -783,7 +698,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -806,19 +721,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>利用能量技术制造的光剑</t>
+          <t>利用能量技术制造的光刃武器</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WPN002</t>
+          <t>WPN004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>制式军刀</t>
+          <t>雷霆战斧</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -828,20 +743,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -851,19 +766,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>标准配置的军用武器</t>
+          <t>附带雷电属性的战斧</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WPN004</t>
+          <t>WPN005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>雷霆之怒</t>
+          <t>暗影匕首</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -873,42 +788,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.05</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>雷电属性的高级武器</t>
+          <t>废土刺客公会的制式武器</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WPN003</t>
+          <t>WPN006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>能量光剑</t>
+          <t>元素法杖</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -918,20 +833,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -941,19 +856,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>利用能量技术制造的光剑</t>
+          <t>蕴含元素之力的科技法杖</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WPN005</t>
+          <t>WPN007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>暗影匕首</t>
+          <t>铁血巨剑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -963,42 +878,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.05</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>刺客公会流传的暗杀武器</t>
+          <t>传说中铁血战将的佩剑</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WPN004</t>
+          <t>WPN008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>雷霆之怒</t>
+          <t>虚空撕裂者</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1008,20 +923,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1031,19 +946,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>雷电属性的高级武器</t>
+          <t>能够撕裂空间的实验武器</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WPN006</t>
+          <t>WPN009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>元素法杖</t>
+          <t>不灭之光</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1053,110 +968,110 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>蕴含元素之力的法杖</t>
+          <t>蕴含不灭能量的终极武器</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WPN005</t>
+          <t>ARM001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>暗影匕首</t>
+          <t>破旧皮甲</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>刺客公会流传的暗杀武器</t>
+          <t>勉强能穿的防护装备</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WPN007</t>
+          <t>ARM002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>战神巨剑</t>
+          <t>标准护甲</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1166,244 +1081,244 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>传说中的战神佩剑</t>
+          <t>标准配置的防护装备</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WPN006</t>
+          <t>ARM003</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元素法杖</t>
+          <t>能量护盾甲</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>蕴含元素之力的法杖</t>
+          <t>配备能量护盾的护甲</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WPN008</t>
+          <t>ARM004</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>虚空撕裂者</t>
+          <t>钢铁壁垒</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.12</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>能够撕裂次元的武器</t>
+          <t>重型防护装备</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WPN007</t>
+          <t>ARM005</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>战神巨剑</t>
+          <t>暗影斗篷</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>传说中的战神佩剑</t>
+          <t>能够隐匿身形的护甲</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WPN009</t>
+          <t>ARM006</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>永恒之光</t>
+          <t>元素之铠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>mythic</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0.05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>蕴含创世力量的神器</t>
+          <t>蕴含元素防护的护甲</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WPN008</t>
+          <t>ARM007</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>虚空撕裂者</t>
+          <t>铁血护甲</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>能够撕裂次元的武器</t>
+          <t>铁血战将传承的防护装备</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARM001</t>
+          <t>ARM008</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>破旧皮甲</t>
+          <t>虚空铠甲</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1413,17 +1328,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1432,307 +1347,307 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>勉强能穿的防护装备</t>
+          <t>来自虚空的防护铠甲</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WPN009</t>
+          <t>ARM009</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>永恒之光</t>
+          <t>不灭守护</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>mythic</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="H21" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>蕴含创世力量的神器</t>
+          <t>不灭守护者的终极护甲</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARM002</t>
+          <t>ACC001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>标准护甲</t>
+          <t>旧戒指</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>标准配置的防护装备</t>
+          <t>一枚普通的旧戒指</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ARM001</t>
+          <t>ACC002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>破旧皮甲</t>
+          <t>能量吊坠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>勉强能穿的防护装备</t>
+          <t>蕴含微弱能量的饰品</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ARM003</t>
+          <t>ACC003</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>能量护盾</t>
+          <t>暴击戒指</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>配备能量护盾的护甲</t>
+          <t>提升暴击率的戒指</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARM002</t>
+          <t>ACC004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>标准护甲</t>
+          <t>闪避项链</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>标准配置的防护装备</t>
+          <t>提升闪避率的项链</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARM004</t>
+          <t>ACC005</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>钢铁壁垒</t>
+          <t>暴怒指虎</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>重型防护装备</t>
+          <t>野兽风格的战斗饰品</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARM003</t>
+          <t>ACC006</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>能量护盾</t>
+          <t>生命护符</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1741,1323 +1656,152 @@
         <v>80</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I27" t="n">
         <v>0.03</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>配备能量护盾的护甲</t>
+          <t>大幅提升生命值的护符</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARM005</t>
+          <t>ACC007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>暗影斗篷</t>
+          <t>铁血徽章</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.05</v>
       </c>
-      <c r="I28" t="n">
-        <v>0.08</v>
-      </c>
       <c r="J28" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>能够隐匿身形的护甲</t>
+          <t>铁血战将传承的荣誉徽章</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARM004</t>
+          <t>ACC008</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>钢铁壁垒</t>
+          <t>时空罗盘</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>重型防护装备</t>
+          <t>能够操控时间的实验罗盘</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ARM006</t>
+          <t>ACC009</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>元素之铠</t>
+          <t>不灭之眼</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>蕴含元素防护的护甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ARM005</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>暗影斗篷</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>120</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>能够隐匿身形的护甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ARM007</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>战神护甲</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>200</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>战神传承的防护装备</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ARM006</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>元素之铠</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>150</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>蕴含元素防护的护甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ARM008</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>虚空铠甲</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>250</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>来自虚空的防护铠甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ARM007</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>战神护甲</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>200</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>战神传承的防护装备</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ARM009</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>永恒守护</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>mythic</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>400</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>永恒守护者的神装</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ARM008</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>虚空铠甲</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>4</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>250</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>来自虚空的防护铠甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ACC001</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>旧戒指</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" t="n">
-        <v>10</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>一枚普通的戒指</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ARM009</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>永恒守护</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>armor</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>mythic</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>400</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>永恒守护者的神装</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ACC002</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>能量吊坠</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>蕴含微弱能量的饰品</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ACC001</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>旧戒指</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>10</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>一枚普通的戒指</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ACC003</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>暴击戒指</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" t="n">
-        <v>20</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>提升暴击率的戒指</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ACC002</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>能量吊坠</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
-        <v>15</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>蕴含微弱能量的饰品</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ACC004</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>闪避项链</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>25</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>提升闪避率的项链</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ACC003</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>暴击戒指</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" t="n">
-        <v>20</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>提升暴击率的戒指</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ACC005</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>暴怒指虎</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" t="n">
-        <v>12</v>
-      </c>
-      <c r="G46" t="n">
-        <v>30</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>野兽风格的战斗饰品</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ACC004</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>闪避项链</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>25</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>提升闪避率的项链</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ACC006</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>生命护符</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>80</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>大幅提升生命值的护符</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ACC005</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>暴怒指虎</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" t="n">
-        <v>12</v>
-      </c>
-      <c r="G49" t="n">
-        <v>30</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>野兽风格的战斗饰品</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ACC007</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>战神徽章</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" t="n">
-        <v>50</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>战神传承的荣誉徽章</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ACC006</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>生命护符</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>80</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>大幅提升生命值的护符</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ACC008</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>时空罗盘</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>4</v>
-      </c>
-      <c r="F52" t="n">
-        <v>15</v>
-      </c>
-      <c r="G52" t="n">
-        <v>60</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>能够操控时间的罗盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ACC007</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>战神徽章</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" t="n">
-        <v>20</v>
-      </c>
-      <c r="G53" t="n">
-        <v>50</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>战神传承的荣誉徽章</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ACC009</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>永恒之眼</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>mythic</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>5</v>
-      </c>
-      <c r="F54" t="n">
-        <v>30</v>
-      </c>
-      <c r="G54" t="n">
-        <v>100</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>蕴含宇宙力量的神器</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ACC008</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>时空罗盘</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" t="n">
-        <v>15</v>
-      </c>
-      <c r="G55" t="n">
-        <v>60</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>能够操控时间的罗盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>ACC009</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>永恒之眼</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>mythic</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" t="n">
-        <v>30</v>
-      </c>
-      <c r="G57" t="n">
-        <v>100</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>蕴含宇宙力量的神器</t>
+          <t>蕴含不灭能量的终极饰品</t>
         </is>
       </c>
     </row>
@@ -3365,7 +2109,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>战神套装</t>
+          <t>铁血套装</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3383,7 +2127,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>SSR</t>
         </is>
       </c>
     </row>
@@ -3413,7 +2157,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>SSR</t>
         </is>
       </c>
     </row>
@@ -3443,7 +2187,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
@@ -3473,7 +2217,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SR</t>
         </is>
       </c>
     </row>
@@ -3485,7 +2229,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>永恒套装</t>
+          <t>不灭套装</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3503,7 +2247,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>mythic</t>
+          <t>UR</t>
         </is>
       </c>
     </row>
@@ -3566,7 +2310,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3591,7 +2335,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3616,7 +2360,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3641,7 +2385,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3666,7 +2410,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3691,7 +2435,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3716,7 +2460,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3741,7 +2485,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3766,7 +2510,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3791,7 +2535,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3816,7 +2560,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="D12" t="n">
